--- a/data/trans_orig/IP07KS_C07_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C07_2023-Habitat-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de trato justo por parte de sus padres en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de trato justo por parte de sus padres, percibida por el/la menor en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28934</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21793</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>38069</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>61,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>46,43%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>81,11%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>19552</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15251</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24254</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>62,72%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>48,92%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>77,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>31117</t>
+          <t>21068</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22630</t>
+          <t>15407</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>26020</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>50668</t>
+          <t>50002</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41114</t>
+          <t>41111</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61979</t>
+          <t>61315</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>75,59%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17443</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8348</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24844</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>37,17%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>17,79%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>52,94%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>10529</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6064</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15169</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>33,78%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>19,45%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>48,66%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>11998</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7088</t>
+          <t>7259</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24269</t>
+          <t>17663</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>26301</t>
+          <t>29442</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15247</t>
+          <t>18726</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35342</t>
+          <t>38749</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>47,77%</t>
         </is>
       </c>
     </row>
@@ -946,107 +946,107 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3385</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3640</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,86%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>10,65%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>4205</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>3107</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -1059,107 +1059,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>556</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3334</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3025</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3125</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2967</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1172,107 +1172,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2110</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>6,17%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2275</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>46933</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>46933</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>46933</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>31173</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47424</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47424</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47424</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>78597</t>
+          <t>81114</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>78597</t>
+          <t>81114</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>78597</t>
+          <t>81114</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>55453</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>44992</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>65601</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>54,41%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>44,14%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>64,36%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>32670</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>26551</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>38384</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>60,91%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>49,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>71,57%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>56576</t>
+          <t>34406</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44242</t>
+          <t>27693</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67302</t>
+          <t>40749</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>89245</t>
+          <t>89859</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75926</t>
+          <t>77849</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101883</t>
+          <t>102018</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,1%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>37994</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28624</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>48831</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37,28%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>28,08%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>47,91%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>17654</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12496</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>23701</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>32,92%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>23,3%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,19%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37879</t>
+          <t>19162</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28070</t>
+          <t>12786</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51509</t>
+          <t>25838</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>55533</t>
+          <t>57157</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43240</t>
+          <t>45955</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69135</t>
+          <t>69644</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>43,76%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7846</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3362</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15380</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>15,09%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3309</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1182</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7507</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7700</t>
+          <t>3657</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15458</t>
+          <t>8794</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>11009</t>
+          <t>11503</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18751</t>
+          <t>20447</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -1741,107 +1741,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>630</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3586</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3003</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3246</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3176</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>101924</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>53633</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>102777</t>
+          <t>57225</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>156410</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>156410</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>156410</t>
+          <t>159149</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>49639</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>42256</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>56133</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>76,57%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>65,18%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>86,59%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>33227</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12468</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>55492</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>46,03%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17,27%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>76,88%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>49877</t>
+          <t>33967</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42248</t>
+          <t>26498</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56159</t>
+          <t>39540</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>83104</t>
+          <t>83606</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45966</t>
+          <t>73151</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>106514</t>
+          <t>92514</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>81,05%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11591</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6348</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>18249</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>17,88%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>9,79%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>28,15%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>37800</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>14687</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>58811</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>52,37%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>81,47%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11631</t>
+          <t>14144</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19630</t>
+          <t>21976</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>49432</t>
+          <t>25736</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24823</t>
+          <t>16901</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>88006</t>
+          <t>35061</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>30,72%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>887</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>822</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2712</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>794</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7254</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>11,19%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2539</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2705</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>756</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>7446</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>885</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>72183</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64978</t>
+          <t>49318</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137161</t>
+          <t>114147</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>39692</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>33154</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>45448</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>71,11%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>59,39%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>81,42%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>34523</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>28754</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>40311</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>64,55%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>53,76%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>75,37%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>40398</t>
+          <t>36170</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33321</t>
+          <t>29711</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45604</t>
+          <t>42412</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>74921</t>
+          <t>75862</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>66481</t>
+          <t>66488</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>83640</t>
+          <t>83880</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>11746</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>6790</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>18008</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>21,04%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>12,16%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>32,26%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>16959</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>11910</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>23431</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>31,71%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>22,27%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>43,81%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>11418</t>
+          <t>18462</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>12758</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17560</t>
+          <t>25368</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>28376</t>
+          <t>30208</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20996</t>
+          <t>22775</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>36393</t>
+          <t>38662</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>34,31%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2514</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>6162</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>11,04%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>6185</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>11,56%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>532</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>4705</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -3218,107 +3218,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5877</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>10,53%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1852</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>6431</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1868</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>5636</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>11,41%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1852</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6084</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>55820</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>53483</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56865</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>112685</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>112685</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>112685</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>173717</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>158483</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>190640</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>64,46%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>58,81%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>70,74%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>119971</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>77142</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>142857</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>57,0%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>36,65%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>67,87%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>177968</t>
+          <t>125611</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>160102</t>
+          <t>112461</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>196191</t>
+          <t>137135</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>297939</t>
+          <t>299328</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>244150</t>
+          <t>278565</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>323177</t>
+          <t>319241</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>68,35%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>78774</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>62124</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>94734</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>29,23%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>23,05%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>35,15%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>82942</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>59446</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>128532</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>39,41%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>28,24%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>61,07%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>76700</t>
+          <t>63767</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>60352</t>
+          <t>52548</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>92616</t>
+          <t>76563</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>159642</t>
+          <t>142542</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>131933</t>
+          <t>124656</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>215864</t>
+          <t>162755</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>11247</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>5942</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>19873</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>6678</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>3019</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>13389</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11168</t>
+          <t>7462</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5707</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19458</t>
+          <t>12751</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>17846</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>27153</t>
+          <t>27953</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -3787,107 +3787,107 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>4234</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>3660</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>4252</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>3755</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>4580</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>1714</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>9660</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>881</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>2735</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>2712</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>4557</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>10860</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2235</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>11142</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>269506</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>269506</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>269506</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>271551</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>271551</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>271551</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>482023</t>
+          <t>467094</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>482023</t>
+          <t>467094</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>482023</t>
+          <t>467094</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
